--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260708.xlsx
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
